--- a/Notebooks/data_processed.xlsx
+++ b/Notebooks/data_processed.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE161"/>
+  <dimension ref="A1:AG161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -586,6 +586,16 @@
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>area_max_um</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>time_wave_start_guess</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>time_wave_arrival_guess</t>
         </is>
       </c>
     </row>
@@ -759,6 +769,12 @@
       <c r="AE2" t="n">
         <v>106182.5184</v>
       </c>
+      <c r="AF2" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>124</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -934,6 +950,12 @@
       <c r="AE3" t="n">
         <v>152582.1372</v>
       </c>
+      <c r="AF3" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>132</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -1109,6 +1131,12 @@
       <c r="AE4" t="n">
         <v>140972.8104</v>
       </c>
+      <c r="AF4" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -1280,6 +1308,12 @@
       <c r="AE5" t="n">
         <v>102700.89</v>
       </c>
+      <c r="AF5" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -1455,6 +1489,12 @@
       <c r="AE6" t="n">
         <v>133640.4672</v>
       </c>
+      <c r="AF6" t="n">
+        <v>43</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1626,6 +1666,12 @@
       <c r="AE7" t="n">
         <v>107074.044</v>
       </c>
+      <c r="AF7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1797,6 +1843,8 @@
       <c r="AE8" t="n">
         <v>57751.62479999999</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1960,6 +2008,8 @@
       <c r="AE9" t="n">
         <v>35698.7124</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -2131,6 +2181,12 @@
       <c r="AE10" t="n">
         <v>149308.4448</v>
       </c>
+      <c r="AF10" t="n">
+        <v>53</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2306,6 +2362,12 @@
       <c r="AE11" t="n">
         <v>838605.1500000001</v>
       </c>
+      <c r="AF11" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -2479,6 +2541,12 @@
       <c r="AE12" t="n">
         <v>698360.1300000001</v>
       </c>
+      <c r="AF12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>204</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -2654,6 +2722,12 @@
       <c r="AE13" t="n">
         <v>476031.5325000001</v>
       </c>
+      <c r="AF13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>197</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -2829,6 +2903,12 @@
       <c r="AE14" t="n">
         <v>288201.8952</v>
       </c>
+      <c r="AF14" t="n">
+        <v>37</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -3004,6 +3084,12 @@
       <c r="AE15" t="n">
         <v>379745.7191999999</v>
       </c>
+      <c r="AF15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -3179,6 +3265,12 @@
       <c r="AE16" t="n">
         <v>431803.7963999999</v>
       </c>
+      <c r="AF16" t="n">
+        <v>31</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -3354,6 +3446,12 @@
       <c r="AE17" t="n">
         <v>351614.5776</v>
       </c>
+      <c r="AF17" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -3529,6 +3627,12 @@
       <c r="AE18" t="n">
         <v>359494.0524</v>
       </c>
+      <c r="AF18" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -3704,6 +3808,12 @@
       <c r="AE19" t="n">
         <v>390003.4619999999</v>
       </c>
+      <c r="AF19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -3879,6 +3989,8 @@
       <c r="AE20" t="n">
         <v>938720.5425000001</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -4054,6 +4166,12 @@
       <c r="AE21" t="n">
         <v>688103.1000000001</v>
       </c>
+      <c r="AF21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>202</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -4229,6 +4347,12 @@
       <c r="AE22" t="n">
         <v>785478.2399999999</v>
       </c>
+      <c r="AF22" t="n">
+        <v>89</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -4404,6 +4528,12 @@
       <c r="AE23" t="n">
         <v>1100212.7688</v>
       </c>
+      <c r="AF23" t="n">
+        <v>113</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -4579,6 +4709,12 @@
       <c r="AE24" t="n">
         <v>1011855.564</v>
       </c>
+      <c r="AF24" t="n">
+        <v>119</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -4754,6 +4890,12 @@
       <c r="AE25" t="n">
         <v>294782.085</v>
       </c>
+      <c r="AF25" t="n">
+        <v>62</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -4929,6 +5071,12 @@
       <c r="AE26" t="n">
         <v>295660.53</v>
       </c>
+      <c r="AF26" t="n">
+        <v>57</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>173</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -5104,6 +5252,12 @@
       <c r="AE27" t="n">
         <v>310851.0675000001</v>
       </c>
+      <c r="AF27" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
@@ -5279,6 +5433,12 @@
       <c r="AE28" t="n">
         <v>312422.0625000001</v>
       </c>
+      <c r="AF28" t="n">
+        <v>63</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
@@ -5454,6 +5614,12 @@
       <c r="AE29" t="n">
         <v>333923.9175</v>
       </c>
+      <c r="AF29" t="n">
+        <v>62</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>208</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -5629,6 +5795,12 @@
       <c r="AE30" t="n">
         <v>479357.5950000001</v>
       </c>
+      <c r="AF30" t="n">
+        <v>61</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
@@ -5804,6 +5976,12 @@
       <c r="AE31" t="n">
         <v>694449.045</v>
       </c>
+      <c r="AF31" t="n">
+        <v>63</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
@@ -5979,6 +6157,12 @@
       <c r="AE32" t="n">
         <v>298633.0275</v>
       </c>
+      <c r="AF32" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
@@ -6154,6 +6338,12 @@
       <c r="AE33" t="n">
         <v>313335.1350000001</v>
       </c>
+      <c r="AF33" t="n">
+        <v>59</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>207</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
@@ -6329,6 +6519,12 @@
       <c r="AE34" t="n">
         <v>571916.9025000001</v>
       </c>
+      <c r="AF34" t="n">
+        <v>56</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
@@ -6503,6 +6699,12 @@
       </c>
       <c r="AE35" t="n">
         <v>274891.32</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>64</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>215</v>
       </c>
     </row>
     <row r="36">
@@ -6700,6 +6902,12 @@
       <c r="AE36" t="n">
         <v>909584.8415999999</v>
       </c>
+      <c r="AF36" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
@@ -6896,6 +7104,12 @@
       <c r="AE37" t="n">
         <v>655344.0935999999</v>
       </c>
+      <c r="AF37" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -7092,6 +7306,12 @@
       <c r="AE38" t="n">
         <v>750003.0587999999</v>
       </c>
+      <c r="AF38" t="n">
+        <v>64</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
@@ -7288,6 +7508,12 @@
       <c r="AE39" t="n">
         <v>749138.8247999999</v>
       </c>
+      <c r="AF39" t="n">
+        <v>81</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
@@ -7484,6 +7710,12 @@
       <c r="AE40" t="n">
         <v>433356.8183999999</v>
       </c>
+      <c r="AF40" t="n">
+        <v>80</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
@@ -7680,6 +7912,12 @@
       <c r="AE41" t="n">
         <v>661253.3747999999</v>
       </c>
+      <c r="AF41" t="n">
+        <v>63</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
@@ -7876,6 +8114,12 @@
       <c r="AE42" t="n">
         <v>846586.7315999999</v>
       </c>
+      <c r="AF42" t="n">
+        <v>124</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>287</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
@@ -8047,6 +8291,12 @@
       <c r="AE43" t="n">
         <v>145173.06</v>
       </c>
+      <c r="AF43" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -8218,6 +8468,12 @@
       <c r="AE44" t="n">
         <v>163729.755</v>
       </c>
+      <c r="AF44" t="n">
+        <v>43</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>137</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
@@ -8389,6 +8645,12 @@
       <c r="AE45" t="n">
         <v>101137.815</v>
       </c>
+      <c r="AF45" t="n">
+        <v>49</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
@@ -8560,6 +8822,12 @@
       <c r="AE46" t="n">
         <v>93403.12500000001</v>
       </c>
+      <c r="AF46" t="n">
+        <v>37</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
@@ -8731,6 +8999,12 @@
       <c r="AE47" t="n">
         <v>86142.28500000002</v>
       </c>
+      <c r="AF47" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>119</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
@@ -8902,6 +9176,12 @@
       <c r="AE48" t="n">
         <v>89112.96000000001</v>
       </c>
+      <c r="AF48" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -9073,6 +9353,12 @@
       <c r="AE49" t="n">
         <v>91786.5675</v>
       </c>
+      <c r="AF49" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
@@ -9244,6 +9530,12 @@
       <c r="AE50" t="n">
         <v>110503.6425</v>
       </c>
+      <c r="AF50" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>130</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
@@ -9415,6 +9707,12 @@
       <c r="AE51" t="n">
         <v>142902.225</v>
       </c>
+      <c r="AF51" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
@@ -9586,6 +9884,12 @@
       <c r="AE52" t="n">
         <v>141376.7925</v>
       </c>
+      <c r="AF52" t="n">
+        <v>41</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
@@ -9757,6 +10061,12 @@
       <c r="AE53" t="n">
         <v>164052.3375</v>
       </c>
+      <c r="AF53" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
@@ -9919,6 +10229,12 @@
       </c>
       <c r="AE54" t="n">
         <v>48310.83000000001</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>111</v>
       </c>
     </row>
     <row r="55">
@@ -10091,6 +10407,12 @@
       <c r="AE55" t="n">
         <v>106572.51</v>
       </c>
+      <c r="AF55" t="n">
+        <v>51</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>134</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
@@ -10262,6 +10584,12 @@
       <c r="AE56" t="n">
         <v>93742.11000000002</v>
       </c>
+      <c r="AF56" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG56" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
@@ -10433,6 +10761,12 @@
       <c r="AE57" t="n">
         <v>57301.22250000001</v>
       </c>
+      <c r="AF57" t="n">
+        <v>57</v>
+      </c>
+      <c r="AG57" t="n">
+        <v>112</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
@@ -10608,6 +10942,8 @@
       <c r="AE58" t="n">
         <v>330453.1908</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
@@ -10783,6 +11119,8 @@
       <c r="AE59" t="n">
         <v>406917.7559999999</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
@@ -10958,6 +11296,8 @@
       <c r="AE60" t="n">
         <v>254882.7504</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
@@ -11133,6 +11473,8 @@
       <c r="AE61" t="n">
         <v>502882.8192</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
@@ -11308,6 +11650,8 @@
       <c r="AE62" t="n">
         <v>359027.496</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
@@ -11483,6 +11827,8 @@
       <c r="AE63" t="n">
         <v>298498.626</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
@@ -11658,6 +12004,8 @@
       <c r="AE64" t="n">
         <v>311671.3716</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
@@ -11833,6 +12181,8 @@
       <c r="AE65" t="n">
         <v>257149.2528</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
@@ -12008,6 +12358,8 @@
       <c r="AE66" t="n">
         <v>303203.178</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
@@ -12183,6 +12535,8 @@
       <c r="AE67" t="n">
         <v>363919.1904</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
@@ -12358,6 +12712,8 @@
       <c r="AE68" t="n">
         <v>310804.5384</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
+      <c r="AG68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
@@ -12533,6 +12889,8 @@
       <c r="AE69" t="n">
         <v>452159.4311999999</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
+      <c r="AG69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
@@ -12708,6 +13066,8 @@
       <c r="AE70" t="n">
         <v>330128.2908</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
@@ -12883,6 +13243,8 @@
       <c r="AE71" t="n">
         <v>379494.8964</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
@@ -13058,6 +13420,8 @@
       <c r="AE72" t="n">
         <v>396756.1835999999</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
@@ -13233,6 +13597,12 @@
       <c r="AE73" t="n">
         <v>213675.3675</v>
       </c>
+      <c r="AF73" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG73" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
@@ -13408,6 +13778,12 @@
       <c r="AE74" t="n">
         <v>209274.03</v>
       </c>
+      <c r="AF74" t="n">
+        <v>49</v>
+      </c>
+      <c r="AG74" t="n">
+        <v>178</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
@@ -13583,6 +13959,12 @@
       <c r="AE75" t="n">
         <v>271370.2500000001</v>
       </c>
+      <c r="AF75" t="n">
+        <v>51</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -13758,6 +14140,12 @@
       <c r="AE76" t="n">
         <v>258665.6025</v>
       </c>
+      <c r="AF76" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG76" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -13933,6 +14321,12 @@
       <c r="AE77" t="n">
         <v>336976.605</v>
       </c>
+      <c r="AF77" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG77" t="n">
+        <v>210</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -14108,6 +14502,12 @@
       <c r="AE78" t="n">
         <v>374720.5800000001</v>
       </c>
+      <c r="AF78" t="n">
+        <v>51</v>
+      </c>
+      <c r="AG78" t="n">
+        <v>194</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
@@ -14283,6 +14683,12 @@
       <c r="AE79" t="n">
         <v>185780.1825</v>
       </c>
+      <c r="AF79" t="n">
+        <v>49</v>
+      </c>
+      <c r="AG79" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
@@ -14454,6 +14860,12 @@
       <c r="AE80" t="n">
         <v>160655.1975</v>
       </c>
+      <c r="AF80" t="n">
+        <v>47</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
@@ -14625,6 +15037,12 @@
       <c r="AE81" t="n">
         <v>166660.335</v>
       </c>
+      <c r="AF81" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG81" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
@@ -14800,6 +15218,12 @@
       <c r="AE82" t="n">
         <v>200456.775</v>
       </c>
+      <c r="AF82" t="n">
+        <v>49</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
@@ -14975,6 +15399,12 @@
       <c r="AE83" t="n">
         <v>207719.4375</v>
       </c>
+      <c r="AF83" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
@@ -15146,6 +15576,12 @@
       <c r="AE84" t="n">
         <v>174261.9825</v>
       </c>
+      <c r="AF84" t="n">
+        <v>76</v>
+      </c>
+      <c r="AG84" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
@@ -15321,6 +15757,12 @@
       <c r="AE85" t="n">
         <v>200021.1975</v>
       </c>
+      <c r="AF85" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
@@ -15496,6 +15938,12 @@
       <c r="AE86" t="n">
         <v>231636.105</v>
       </c>
+      <c r="AF86" t="n">
+        <v>88</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>168</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
@@ -15671,6 +16119,12 @@
       <c r="AE87" t="n">
         <v>273808.7550000001</v>
       </c>
+      <c r="AF87" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
@@ -15846,6 +16300,12 @@
       <c r="AE88" t="n">
         <v>323497.395</v>
       </c>
+      <c r="AF88" t="n">
+        <v>91</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
@@ -16021,6 +16481,12 @@
       <c r="AE89" t="n">
         <v>248155.245</v>
       </c>
+      <c r="AF89" t="n">
+        <v>92</v>
+      </c>
+      <c r="AG89" t="n">
+        <v>166</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
@@ -16196,6 +16662,12 @@
       <c r="AE90" t="n">
         <v>248844.15</v>
       </c>
+      <c r="AF90" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG90" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
@@ -16371,6 +16843,12 @@
       <c r="AE91" t="n">
         <v>237898.215</v>
       </c>
+      <c r="AF91" t="n">
+        <v>72</v>
+      </c>
+      <c r="AG91" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
@@ -16542,6 +17020,12 @@
       <c r="AE92" t="n">
         <v>176068.08</v>
       </c>
+      <c r="AF92" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
@@ -16717,6 +17201,12 @@
       <c r="AE93" t="n">
         <v>202292.0325</v>
       </c>
+      <c r="AF93" t="n">
+        <v>74</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
@@ -16888,6 +17378,12 @@
       <c r="AE94" t="n">
         <v>124327.305</v>
       </c>
+      <c r="AF94" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG94" t="n">
+        <v>167</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
@@ -17059,6 +17555,12 @@
       <c r="AE95" t="n">
         <v>172532.43</v>
       </c>
+      <c r="AF95" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
@@ -17230,6 +17732,12 @@
       <c r="AE96" t="n">
         <v>160133.9625</v>
       </c>
+      <c r="AF96" t="n">
+        <v>88</v>
+      </c>
+      <c r="AG96" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
@@ -17405,6 +17913,12 @@
       <c r="AE97" t="n">
         <v>205490.52</v>
       </c>
+      <c r="AF97" t="n">
+        <v>89</v>
+      </c>
+      <c r="AG97" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
@@ -17580,6 +18094,12 @@
       <c r="AE98" t="n">
         <v>569330.775</v>
       </c>
+      <c r="AF98" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG98" t="n">
+        <v>215</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
@@ -17755,6 +18275,12 @@
       <c r="AE99" t="n">
         <v>457555.0275000001</v>
       </c>
+      <c r="AF99" t="n">
+        <v>43</v>
+      </c>
+      <c r="AG99" t="n">
+        <v>196</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
@@ -17930,6 +18456,12 @@
       <c r="AE100" t="n">
         <v>343721.6775</v>
       </c>
+      <c r="AF100" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG100" t="n">
+        <v>187</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
@@ -18105,6 +18637,12 @@
       <c r="AE101" t="n">
         <v>415863.5175000001</v>
       </c>
+      <c r="AF101" t="n">
+        <v>46</v>
+      </c>
+      <c r="AG101" t="n">
+        <v>203</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
@@ -18280,6 +18818,12 @@
       <c r="AE102" t="n">
         <v>339076.1250000001</v>
       </c>
+      <c r="AF102" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG102" t="n">
+        <v>201</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
@@ -18455,6 +18999,12 @@
       <c r="AE103" t="n">
         <v>355012.0650000001</v>
       </c>
+      <c r="AF103" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG103" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
@@ -18630,6 +19180,12 @@
       <c r="AE104" t="n">
         <v>247340.5875</v>
       </c>
+      <c r="AF104" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
@@ -18805,6 +19361,12 @@
       <c r="AE105" t="n">
         <v>247674.105</v>
       </c>
+      <c r="AF105" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG105" t="n">
+        <v>126</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
@@ -18980,6 +19542,12 @@
       <c r="AE106" t="n">
         <v>246485.835</v>
       </c>
+      <c r="AF106" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG106" t="n">
+        <v>131</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
@@ -19155,6 +19723,12 @@
       <c r="AE107" t="n">
         <v>197600.9175</v>
       </c>
+      <c r="AF107" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG107" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
@@ -19326,6 +19900,12 @@
       <c r="AE108" t="n">
         <v>161180.0775</v>
       </c>
+      <c r="AF108" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG108" t="n">
+        <v>129</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
@@ -19497,6 +20077,12 @@
       <c r="AE109" t="n">
         <v>175512.2175</v>
       </c>
+      <c r="AF109" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG109" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
@@ -19672,6 +20258,12 @@
       <c r="AE110" t="n">
         <v>366411.8025</v>
       </c>
+      <c r="AF110" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG110" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
@@ -19843,6 +20435,12 @@
       <c r="AE111" t="n">
         <v>177174.3375</v>
       </c>
+      <c r="AF111" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG111" t="n">
+        <v>123</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
@@ -20014,6 +20612,12 @@
       <c r="AE112" t="n">
         <v>179791.4475</v>
       </c>
+      <c r="AF112" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG112" t="n">
+        <v>118</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
@@ -20189,6 +20793,12 @@
       <c r="AE113" t="n">
         <v>196326.99</v>
       </c>
+      <c r="AF113" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
@@ -20364,6 +20974,12 @@
       <c r="AE114" t="n">
         <v>324049.6125</v>
       </c>
+      <c r="AF114" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG114" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
@@ -20539,6 +21155,12 @@
       <c r="AE115" t="n">
         <v>236781.0225</v>
       </c>
+      <c r="AF115" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG115" t="n">
+        <v>125</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
@@ -20714,6 +21336,12 @@
       <c r="AE116" t="n">
         <v>247681.395</v>
       </c>
+      <c r="AF116" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG116" t="n">
+        <v>127</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
@@ -20884,6 +21512,12 @@
       </c>
       <c r="AE117" t="n">
         <v>139608.9675</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>50</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>132</v>
       </c>
     </row>
     <row r="118">
@@ -21114,6 +21748,12 @@
       <c r="AE118" t="n">
         <v>225465.0048</v>
       </c>
+      <c r="AF118" t="n">
+        <v>51</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
@@ -21343,6 +21983,12 @@
       <c r="AE119" t="n">
         <v>243289.0188</v>
       </c>
+      <c r="AF119" t="n">
+        <v>52</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
@@ -21572,6 +22218,12 @@
       <c r="AE120" t="n">
         <v>262864.8936</v>
       </c>
+      <c r="AF120" t="n">
+        <v>54</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>169</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
@@ -21801,6 +22453,12 @@
       <c r="AE121" t="n">
         <v>209466.9288</v>
       </c>
+      <c r="AF121" t="n">
+        <v>54</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>163</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
@@ -22030,6 +22688,12 @@
       <c r="AE122" t="n">
         <v>170459.4348</v>
       </c>
+      <c r="AF122" t="n">
+        <v>62</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
@@ -22259,6 +22923,8 @@
       <c r="AE123" t="n">
         <v>263840.8932</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
@@ -22488,6 +23154,8 @@
       <c r="AE124" t="n">
         <v>321495.048</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
@@ -22717,6 +23385,8 @@
       <c r="AE125" t="n">
         <v>369213.7608</v>
       </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
@@ -22946,6 +23616,8 @@
       <c r="AE126" t="n">
         <v>349323.3828</v>
       </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
@@ -23169,6 +23841,8 @@
       <c r="AE127" t="n">
         <v>114398.5896</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
@@ -23398,6 +24072,8 @@
       <c r="AE128" t="n">
         <v>174633.75</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
@@ -23627,6 +24303,8 @@
       <c r="AE129" t="n">
         <v>209518.9128</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
@@ -23856,6 +24534,8 @@
       <c r="AE130" t="n">
         <v>217321.7112</v>
       </c>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
@@ -24085,6 +24765,8 @@
       <c r="AE131" t="n">
         <v>460209.1536</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
@@ -24314,6 +24996,8 @@
       <c r="AE132" t="n">
         <v>336316.986</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
@@ -24543,6 +25227,8 @@
       <c r="AE133" t="n">
         <v>335630.7972</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
@@ -24772,6 +25458,8 @@
       <c r="AE134" t="n">
         <v>386191.7351999999</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
@@ -25001,6 +25689,8 @@
       <c r="AE135" t="n">
         <v>549962.1287999999</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
@@ -25230,6 +25920,8 @@
       <c r="AE136" t="n">
         <v>552840.7427999999</v>
       </c>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
@@ -25459,6 +26151,8 @@
       <c r="AE137" t="n">
         <v>244268.9172</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
@@ -25691,6 +26385,12 @@
       <c r="AE138" t="n">
         <v>207132.5925</v>
       </c>
+      <c r="AF138" t="n">
+        <v>45</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
@@ -25923,6 +26623,12 @@
       <c r="AE139" t="n">
         <v>188898.48</v>
       </c>
+      <c r="AF139" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>166</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
@@ -26155,6 +26861,12 @@
       <c r="AE140" t="n">
         <v>219560.22</v>
       </c>
+      <c r="AF140" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
@@ -26387,6 +27099,12 @@
       <c r="AE141" t="n">
         <v>240710.3325</v>
       </c>
+      <c r="AF141" t="n">
+        <v>41</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>161</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
@@ -26619,6 +27337,12 @@
       <c r="AE142" t="n">
         <v>195089.5125</v>
       </c>
+      <c r="AF142" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
@@ -26851,6 +27575,12 @@
       <c r="AE143" t="n">
         <v>195078.5775</v>
       </c>
+      <c r="AF143" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>128</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
@@ -27083,6 +27813,12 @@
       <c r="AE144" t="n">
         <v>400895.3250000001</v>
       </c>
+      <c r="AF144" t="n">
+        <v>27</v>
+      </c>
+      <c r="AG144" t="n">
+        <v>165</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
@@ -27315,6 +28051,12 @@
       <c r="AE145" t="n">
         <v>329529.8700000001</v>
       </c>
+      <c r="AF145" t="n">
+        <v>35</v>
+      </c>
+      <c r="AG145" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
@@ -27547,6 +28289,12 @@
       <c r="AE146" t="n">
         <v>252946.5975</v>
       </c>
+      <c r="AF146" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG146" t="n">
+        <v>133</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
@@ -27779,6 +28527,12 @@
       <c r="AE147" t="n">
         <v>332442.225</v>
       </c>
+      <c r="AF147" t="n">
+        <v>76</v>
+      </c>
+      <c r="AG147" t="n">
+        <v>213</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
@@ -28004,6 +28758,12 @@
       <c r="AE148" t="n">
         <v>148107.285</v>
       </c>
+      <c r="AF148" t="n">
+        <v>78</v>
+      </c>
+      <c r="AG148" t="n">
+        <v>188</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
@@ -28227,6 +28987,12 @@
       <c r="AE149" t="n">
         <v>102734.325</v>
       </c>
+      <c r="AF149" t="n">
+        <v>77</v>
+      </c>
+      <c r="AG149" t="n">
+        <v>164</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
@@ -28452,6 +29218,12 @@
       <c r="AE150" t="n">
         <v>107294.22</v>
       </c>
+      <c r="AF150" t="n">
+        <v>87</v>
+      </c>
+      <c r="AG150" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
@@ -28675,6 +29447,12 @@
       <c r="AE151" t="n">
         <v>139559.76</v>
       </c>
+      <c r="AF151" t="n">
+        <v>81</v>
+      </c>
+      <c r="AG151" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
@@ -28900,6 +29678,12 @@
       <c r="AE152" t="n">
         <v>159151.635</v>
       </c>
+      <c r="AF152" t="n">
+        <v>84</v>
+      </c>
+      <c r="AG152" t="n">
+        <v>188</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
@@ -29132,6 +29916,12 @@
       <c r="AE153" t="n">
         <v>222148.17</v>
       </c>
+      <c r="AF153" t="n">
+        <v>79</v>
+      </c>
+      <c r="AG153" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
@@ -29357,6 +30147,12 @@
       <c r="AE154" t="n">
         <v>175945.9725</v>
       </c>
+      <c r="AF154" t="n">
+        <v>76</v>
+      </c>
+      <c r="AG154" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
@@ -29582,6 +30378,12 @@
       <c r="AE155" t="n">
         <v>170476.65</v>
       </c>
+      <c r="AF155" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG155" t="n">
+        <v>171</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
@@ -29807,6 +30609,12 @@
       <c r="AE156" t="n">
         <v>154832.31</v>
       </c>
+      <c r="AF156" t="n">
+        <v>66</v>
+      </c>
+      <c r="AG156" t="n">
+        <v>181</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
@@ -30032,6 +30840,12 @@
       <c r="AE157" t="n">
         <v>179177.265</v>
       </c>
+      <c r="AF157" t="n">
+        <v>68</v>
+      </c>
+      <c r="AG157" t="n">
+        <v>198</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
@@ -30264,6 +31078,12 @@
       <c r="AE158" t="n">
         <v>195920.5725</v>
       </c>
+      <c r="AF158" t="n">
+        <v>69</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>182</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
@@ -30496,6 +31316,12 @@
       <c r="AE159" t="n">
         <v>216558.5625</v>
       </c>
+      <c r="AF159" t="n">
+        <v>39</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>136</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
@@ -30728,6 +31554,12 @@
       <c r="AE160" t="n">
         <v>196071.84</v>
       </c>
+      <c r="AF160" t="n">
+        <v>75</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>191</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
@@ -30939,6 +31771,12 @@
       <c r="AE161" t="n">
         <v>44840.79000000001</v>
       </c>
+      <c r="AF161" t="n">
+        <v>82</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>125</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
